--- a/data/trans_dic/IP31KM10_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 37,67</t>
+          <t>27,88; 50,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,34; 47,52</t>
+          <t>17,98; 38,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 39,14</t>
+          <t>25,95; 41,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,69; 58,14</t>
+          <t>48,99; 61,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,73; 60,65</t>
+          <t>43,09; 56,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49,01; 57,77</t>
+          <t>48,04; 56,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,39; 62,78</t>
+          <t>48,94; 62,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 62,09</t>
+          <t>50,63; 63,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,52; 60,75</t>
+          <t>51,96; 61,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,3; 68,52</t>
+          <t>57,01; 68,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,39; 67,27</t>
+          <t>46,37; 57,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,24; 65,57</t>
+          <t>53,62; 61,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,56; 58,75</t>
+          <t>54,18; 61,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,95; 60,33</t>
+          <t>47,92; 54,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,98; 58,06</t>
+          <t>52,35; 57,17</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>26262</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8135; 17514</t>
+          <t>10435; 19085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11477; 21517</t>
+          <t>7675; 16446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22173; 35923</t>
+          <t>20790; 33638</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>87741</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100914</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182236</t>
+          <t>159675</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71188; 92623</t>
+          <t>76933; 96174</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88664; 110353</t>
+          <t>62706; 81514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167255; 197156</t>
+          <t>145350; 172381</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>133</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98127</t>
+          <t>111217</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116917</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215044</t>
+          <t>211666</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85481; 108659</t>
+          <t>97945; 124299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103245; 131941</t>
+          <t>88444; 110618</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>198638; 234243</t>
+          <t>194752; 228916</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>173</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>150707</t>
+          <t>183449</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>185807</t>
+          <t>132693</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336514</t>
+          <t>316143</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129735; 187929</t>
+          <t>166593; 201296</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165903; 205163</t>
+          <t>118391; 146953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>308413; 379826</t>
+          <t>293589; 339017</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>459</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>342390</t>
+          <t>396963</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>762210</t>
+          <t>713745</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>317176; 383688</t>
+          <t>372106; 422138</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>394361; 449275</t>
+          <t>296244; 339309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>726618; 811629</t>
+          <t>683147; 746073</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM10_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman frutos secos con regularidad (al menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>38,88%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>27,88; 50,98</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17,98; 38,53</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25,95; 41,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>55,87%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>48,99; 61,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43,09; 56,02</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>48,04; 56,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>55,57%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>48,94; 62,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>50,63; 63,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>51,96; 61,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>62,78%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51,97%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>57,01; 68,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>46,37; 57,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53,62; 61,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>54,18; 61,46</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>47,92; 54,89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52,35; 57,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.3888296949636376</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2742621496176901</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3277952533902303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>14556</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11706</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26262</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2787592975894302</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1798231227995445</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2594983969558846</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10435; 19085</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7675; 16446</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20790; 33638</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5098112591664299</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.385329020524708</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4198601009052351</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5587122294803641</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.494331152515706</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5277478156592236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>87741</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>71934</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159675</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4898899648943853</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4309191345445881</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4803990890901518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>76933; 96174</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>62706; 81514</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>145350; 172381</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6124096092206052</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5601625086896412</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5697422839895528</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5557340157994674</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5750716127960477</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5647461800984983</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>111217</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>100449</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>211666</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4894169702977577</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5063460401359436</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5196175195977731</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>97945; 124299</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>88444; 110618</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>194752; 228916</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6211039257640044</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6332923375134871</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6107713448470896</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6277762441694176</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5196792971847944</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5773684932228981</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>183449</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>132693</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>316143</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5700926015646488</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.463665297508622</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5361791483696201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>166593; 201296</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>118391; 146953</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>293589; 339017</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6888474395041188</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5755240966910861</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6191427156918591</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5779695179639944</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5124201323071548</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.546918054504778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>396963</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>316782</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>713745</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5417774523957127</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4791986775420555</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5234715923038582</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>372106; 422138</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>296244; 339309</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>683147; 746073</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.6146233280482842</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5488594877709888</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5716900342889292</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman frutos secos con regularidad (al menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>14556</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11706</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>26262</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>10435</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>7675</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>20790</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>19085</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>16446</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>33638</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>87741</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>71934</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>159675</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>76933</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>62706</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>145350</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>96174</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>81514</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>172381</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>111217</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>100449</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>211666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>97945</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>88444</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>194752</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>124299</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>110618</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>228916</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>183449</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>132693</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>316143</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>166593</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>118391</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>293589</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>201296</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>146953</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>339017</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>519</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>459</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>396963</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>316782</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>713745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>372106</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>296244</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>683147</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>422138</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>339309</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>746073</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>